--- a/data/trans_dic/P0901-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P0901-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,74; 15,55</t>
+          <t>7,64; 15,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,31; 18,27</t>
+          <t>10,25; 18,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,74; 17,35</t>
+          <t>8,99; 16,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 13,09</t>
+          <t>6,19; 12,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,88; 24,9</t>
+          <t>14,96; 24,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,1; 33,01</t>
+          <t>22,02; 33,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,81; 31,44</t>
+          <t>21,56; 32,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,21; 16,05</t>
+          <t>10,26; 16,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,13; 18,68</t>
+          <t>12,67; 18,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,47; 24,77</t>
+          <t>17,47; 24,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,31; 23,26</t>
+          <t>16,05; 22,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,66; 13,26</t>
+          <t>8,85; 13,4</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,13; 12,74</t>
+          <t>7,23; 12,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,28; 14,47</t>
+          <t>8,38; 14,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,28; 11,19</t>
+          <t>6,23; 11,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,21; 21,51</t>
+          <t>13,98; 21,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,78; 21,53</t>
+          <t>14,79; 21,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,77; 22,69</t>
+          <t>15,68; 22,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,33; 20,45</t>
+          <t>13,36; 20,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,34; 27,73</t>
+          <t>21,69; 27,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,66; 16,01</t>
+          <t>11,73; 15,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,42; 17,28</t>
+          <t>12,8; 17,61</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,57; 15,15</t>
+          <t>10,49; 14,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,85; 23,66</t>
+          <t>18,6; 23,38</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 9,35</t>
+          <t>3,81; 9,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,92; 16,79</t>
+          <t>8,88; 16,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 11,78</t>
+          <t>6,1; 12,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,34; 18,58</t>
+          <t>11,39; 18,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,46; 17,66</t>
+          <t>10,39; 17,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,57; 24,32</t>
+          <t>15,7; 24,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,52; 16,17</t>
+          <t>8,97; 16,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,65; 22,41</t>
+          <t>15,8; 22,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,99; 12,9</t>
+          <t>7,87; 12,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,25; 19,14</t>
+          <t>13,49; 19,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,26; 13,09</t>
+          <t>8,32; 13,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,67; 19,6</t>
+          <t>14,59; 19,43</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 8,26</t>
+          <t>3,18; 7,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,41; 20,92</t>
+          <t>12,16; 20,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,35; 21,28</t>
+          <t>13,29; 21,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,65; 25,27</t>
+          <t>15,73; 25,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,64; 20,04</t>
+          <t>12,59; 20,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,27; 37,8</t>
+          <t>28,19; 38,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,38; 37,33</t>
+          <t>28,07; 38,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,35; 26,15</t>
+          <t>12,12; 26,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,66; 13,22</t>
+          <t>8,72; 13,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,37; 27,47</t>
+          <t>21,56; 27,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,51; 28,29</t>
+          <t>21,4; 28,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,57; 24,47</t>
+          <t>14,59; 23,94</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 11,59</t>
+          <t>4,69; 11,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,59; 17,47</t>
+          <t>8,38; 17,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,88; 12,44</t>
+          <t>5,02; 12,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 11,34</t>
+          <t>4,84; 10,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,9; 17,61</t>
+          <t>8,07; 17,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,15; 31,29</t>
+          <t>19,32; 31,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,04; 17,85</t>
+          <t>9,58; 18,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,8; 15,88</t>
+          <t>10,02; 15,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,23; 13,21</t>
+          <t>7,42; 13,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,56; 23,1</t>
+          <t>15,22; 22,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,2; 14,28</t>
+          <t>8,29; 14,45</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,41; 12,57</t>
+          <t>8,31; 12,57</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,75; 14,0</t>
+          <t>6,83; 13,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,76; 17,55</t>
+          <t>9,99; 18,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,66; 21,86</t>
+          <t>12,34; 21,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,44; 16,55</t>
+          <t>9,76; 16,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,85; 21,77</t>
+          <t>12,98; 21,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,76; 22,23</t>
+          <t>13,46; 22,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,36; 29,66</t>
+          <t>19,2; 29,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,87; 20,55</t>
+          <t>14,05; 20,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,97; 16,6</t>
+          <t>10,73; 16,42</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,36; 18,94</t>
+          <t>12,69; 18,64</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,36; 24,57</t>
+          <t>17,22; 24,52</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,5; 17,21</t>
+          <t>12,46; 17,24</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,42; 12,22</t>
+          <t>7,45; 12,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,24; 11,9</t>
+          <t>7,32; 12,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,8; 14,11</t>
+          <t>8,79; 14,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,24; 18,24</t>
+          <t>12,2; 18,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,16; 16,82</t>
+          <t>11,11; 16,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,02; 18,94</t>
+          <t>13,14; 18,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,71; 24,6</t>
+          <t>18,05; 24,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,34; 24,36</t>
+          <t>8,28; 24,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,19; 13,92</t>
+          <t>10,15; 13,57</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,03; 14,58</t>
+          <t>10,88; 14,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,11; 18,38</t>
+          <t>14,07; 18,25</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,36; 20,1</t>
+          <t>10,88; 19,95</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,86; 13,05</t>
+          <t>8,83; 13,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,41; 14,49</t>
+          <t>9,33; 14,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,13; 8,9</t>
+          <t>5,25; 8,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,68; 12,59</t>
+          <t>4,03; 12,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,13; 20,71</t>
+          <t>15,48; 21,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,22; 21,73</t>
+          <t>16,05; 21,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,99; 17,61</t>
+          <t>12,09; 17,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,42; 23,38</t>
+          <t>18,28; 23,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,94; 16,44</t>
+          <t>12,55; 16,31</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13,56; 17,35</t>
+          <t>13,56; 17,38</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,23; 12,62</t>
+          <t>9,21; 12,47</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,3; 16,94</t>
+          <t>8,53; 17,16</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,07; 10,11</t>
+          <t>8,08; 10,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,01; 13,2</t>
+          <t>10,89; 13,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,49; 11,57</t>
+          <t>9,52; 11,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,31; 14,55</t>
+          <t>9,95; 14,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,01; 17,65</t>
+          <t>15,11; 17,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,46; 22,09</t>
+          <t>19,41; 22,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,1; 20,89</t>
+          <t>18,04; 20,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,27; 20,78</t>
+          <t>15,48; 20,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,96; 13,66</t>
+          <t>11,95; 13,53</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15,63; 17,46</t>
+          <t>15,6; 17,43</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14,15; 15,96</t>
+          <t>14,23; 15,97</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,09; 17,3</t>
+          <t>13,91; 17,4</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21121; 42446</t>
+          <t>20862; 41180</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30398; 53848</t>
+          <t>30223; 54643</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25661; 50977</t>
+          <t>26397; 49611</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19466; 40782</t>
+          <t>19294; 39974</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>38825; 64949</t>
+          <t>39034; 64778</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63480; 94806</t>
+          <t>63258; 95536</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60066; 90766</t>
+          <t>62256; 93481</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29584; 46472</t>
+          <t>29713; 47420</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>64731; 99731</t>
+          <t>67616; 100916</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>101663; 144183</t>
+          <t>101674; 140865</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>95014; 135471</t>
+          <t>93501; 133570</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>52034; 79713</t>
+          <t>53212; 80540</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35139; 62831</t>
+          <t>35652; 62751</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41867; 73166</t>
+          <t>42355; 73885</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31537; 56254</t>
+          <t>31304; 55464</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73676; 111485</t>
+          <t>72458; 111667</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74501; 108478</t>
+          <t>74551; 109431</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82579; 118824</t>
+          <t>82134; 118703</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69726; 106946</t>
+          <t>69909; 105567</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>109875; 142825</t>
+          <t>111696; 143132</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>116216; 159587</t>
+          <t>116934; 159351</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>127878; 177885</t>
+          <t>131751; 181269</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>108424; 155395</t>
+          <t>107642; 153624</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>194805; 244509</t>
+          <t>192179; 241598</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12491; 29799</t>
+          <t>12140; 30106</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28916; 54422</t>
+          <t>28764; 54663</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19262; 37537</t>
+          <t>19447; 38889</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35830; 58709</t>
+          <t>36011; 58723</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>35100; 59226</t>
+          <t>34838; 60261</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53098; 82929</t>
+          <t>53532; 84034</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28670; 54397</t>
+          <t>30155; 54811</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>54530; 78113</t>
+          <t>55052; 79434</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>52269; 84399</t>
+          <t>51473; 83241</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>88092; 127309</t>
+          <t>89702; 128408</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54122; 85742</t>
+          <t>54478; 87173</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>97507; 130234</t>
+          <t>96965; 129115</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11384; 29618</t>
+          <t>11396; 28673</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46428; 78222</t>
+          <t>45471; 75189</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49382; 78734</t>
+          <t>49152; 78360</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48840; 78827</t>
+          <t>49071; 80071</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>46938; 74445</t>
+          <t>46757; 76275</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>109970; 147028</t>
+          <t>109659; 147803</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>106048; 144564</t>
+          <t>108718; 147682</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58765; 124395</t>
+          <t>57673; 125729</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>63229; 96523</t>
+          <t>63652; 96248</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>163036; 209588</t>
+          <t>164490; 211332</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>162917; 214257</t>
+          <t>162022; 213097</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>114805; 192713</t>
+          <t>114923; 188602</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9230; 23572</t>
+          <t>9531; 24056</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18258; 37154</t>
+          <t>17819; 37055</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10316; 26275</t>
+          <t>10606; 26698</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8563; 20220</t>
+          <t>8629; 19235</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16401; 36580</t>
+          <t>16754; 35930</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42057; 68711</t>
+          <t>42429; 69070</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19765; 39028</t>
+          <t>20944; 40455</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20345; 32981</t>
+          <t>20819; 32990</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29729; 54305</t>
+          <t>30502; 54332</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67255; 99828</t>
+          <t>65763; 97534</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35263; 61384</t>
+          <t>35649; 62111</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>32440; 48504</t>
+          <t>32063; 48495</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18273; 37914</t>
+          <t>18505; 37380</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26747; 48095</t>
+          <t>27372; 49457</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33314; 57511</t>
+          <t>32471; 56574</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25444; 44634</t>
+          <t>26330; 43865</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>35738; 60541</t>
+          <t>36116; 60607</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35728; 62264</t>
+          <t>37682; 62396</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50149; 80998</t>
+          <t>52439; 81320</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>35659; 52820</t>
+          <t>36120; 53038</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>60194; 91146</t>
+          <t>58925; 90116</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68491; 104935</t>
+          <t>70298; 103275</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93088; 131742</t>
+          <t>92332; 131461</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>65826; 90624</t>
+          <t>65613; 90808</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>45621; 75134</t>
+          <t>45810; 75286</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>47970; 78887</t>
+          <t>48507; 79849</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>57783; 92639</t>
+          <t>57728; 92304</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>76258; 113686</t>
+          <t>75999; 114365</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>71197; 107361</t>
+          <t>70926; 107853</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>90344; 131405</t>
+          <t>91198; 130544</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>122419; 170039</t>
+          <t>124771; 169053</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>79287; 206894</t>
+          <t>70282; 209321</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>127653; 174455</t>
+          <t>127261; 170047</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>149652; 197808</t>
+          <t>147589; 197834</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>190168; 247796</t>
+          <t>189676; 246027</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>152587; 295935</t>
+          <t>160178; 293741</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>65908; 97094</t>
+          <t>65647; 97461</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>73311; 112877</t>
+          <t>72673; 110893</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>39967; 69291</t>
+          <t>40865; 69184</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>34148; 116940</t>
+          <t>37461; 117687</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>118517; 162286</t>
+          <t>121285; 166895</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>133621; 178987</t>
+          <t>132266; 178359</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>99092; 145473</t>
+          <t>99884; 142379</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>132172; 167804</t>
+          <t>131167; 167221</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>197588; 251135</t>
+          <t>191732; 249063</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>217295; 278109</t>
+          <t>217344; 278528</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>148194; 202542</t>
+          <t>147839; 200150</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>136575; 278835</t>
+          <t>140516; 282568</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>264385; 331126</t>
+          <t>264894; 336158</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>377124; 452238</t>
+          <t>373017; 456133</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>322135; 392663</t>
+          <t>323257; 393536</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>356462; 503192</t>
+          <t>344105; 500524</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>507095; 596362</t>
+          <t>510656; 594358</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>692353; 785922</t>
+          <t>690758; 793204</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>641640; 740543</t>
+          <t>639480; 736634</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>559095; 760672</t>
+          <t>566674; 762632</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>795998; 909314</t>
+          <t>795588; 900460</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1091513; 1219392</t>
+          <t>1089810; 1217156</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>981712; 1107494</t>
+          <t>987151; 1107887</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1003297; 1231605</t>
+          <t>990136; 1238738</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P0901-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P0901-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,64; 15,08</t>
+          <t>7,55; 15,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,25; 18,54</t>
+          <t>10,2; 18,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,99; 16,89</t>
+          <t>8,74; 17,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,19; 12,84</t>
+          <t>6,35; 12,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,96; 24,83</t>
+          <t>15,61; 25,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,02; 33,26</t>
+          <t>22,4; 33,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,56; 32,38</t>
+          <t>21,07; 31,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,26; 16,37</t>
+          <t>10,64; 16,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,67; 18,9</t>
+          <t>12,25; 18,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,47; 24,2</t>
+          <t>17,02; 24,28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,05; 22,93</t>
+          <t>15,81; 22,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,85; 13,4</t>
+          <t>9,12; 13,39</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,23; 12,73</t>
+          <t>7,14; 12,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,38; 14,62</t>
+          <t>8,07; 14,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,23; 11,04</t>
+          <t>6,21; 11,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,98; 21,54</t>
+          <t>14,78; 22,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,79; 21,71</t>
+          <t>15,02; 21,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,68; 22,66</t>
+          <t>15,44; 23,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,36; 20,18</t>
+          <t>13,24; 20,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,69; 27,79</t>
+          <t>21,05; 27,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,73; 15,98</t>
+          <t>11,68; 16,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,8; 17,61</t>
+          <t>12,8; 17,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,49; 14,98</t>
+          <t>10,66; 14,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,6; 23,38</t>
+          <t>18,79; 23,86</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 9,44</t>
+          <t>3,79; 9,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,88; 16,87</t>
+          <t>9,06; 16,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,1; 12,21</t>
+          <t>6,05; 12,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,39; 18,58</t>
+          <t>11,14; 17,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,39; 17,97</t>
+          <t>10,18; 17,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,7; 24,64</t>
+          <t>15,65; 24,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,97; 16,3</t>
+          <t>9,0; 16,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,8; 22,79</t>
+          <t>15,53; 21,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,87; 12,72</t>
+          <t>7,96; 12,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,49; 19,31</t>
+          <t>13,21; 19,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,32; 13,31</t>
+          <t>8,19; 13,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,59; 19,43</t>
+          <t>14,32; 18,77</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 7,99</t>
+          <t>3,21; 8,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,16; 20,1</t>
+          <t>12,65; 20,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,29; 21,18</t>
+          <t>13,23; 21,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,73; 25,66</t>
+          <t>14,58; 24,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,59; 20,53</t>
+          <t>13,03; 20,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,19; 38,0</t>
+          <t>27,96; 37,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,07; 38,13</t>
+          <t>27,57; 37,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,12; 26,43</t>
+          <t>21,27; 29,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,72; 13,18</t>
+          <t>8,86; 13,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,56; 27,7</t>
+          <t>21,38; 27,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,4; 28,14</t>
+          <t>21,6; 28,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,59; 23,94</t>
+          <t>19,25; 25,51</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,69; 11,83</t>
+          <t>4,43; 11,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,38; 17,43</t>
+          <t>8,62; 17,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 12,64</t>
+          <t>4,74; 12,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,84; 10,79</t>
+          <t>4,43; 9,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,07; 17,3</t>
+          <t>7,71; 17,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,32; 31,45</t>
+          <t>19,77; 31,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,58; 18,51</t>
+          <t>8,87; 17,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,02; 15,88</t>
+          <t>9,79; 15,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 13,22</t>
+          <t>7,16; 12,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,22; 22,57</t>
+          <t>15,39; 22,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,29; 14,45</t>
+          <t>8,17; 13,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,31; 12,57</t>
+          <t>8,02; 11,84</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,83; 13,8</t>
+          <t>6,92; 14,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,99; 18,05</t>
+          <t>9,91; 17,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,34; 21,5</t>
+          <t>12,65; 21,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,76; 16,27</t>
+          <t>9,03; 15,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,98; 21,79</t>
+          <t>13,21; 21,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,46; 22,28</t>
+          <t>13,0; 21,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,2; 29,77</t>
+          <t>19,62; 30,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,05; 20,63</t>
+          <t>13,77; 20,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,73; 16,42</t>
+          <t>10,96; 16,85</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,69; 18,64</t>
+          <t>12,5; 18,88</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,22; 24,52</t>
+          <t>17,09; 24,63</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,46; 17,24</t>
+          <t>12,12; 16,95</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,45; 12,24</t>
+          <t>7,43; 12,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,32; 12,05</t>
+          <t>7,07; 11,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,79; 14,06</t>
+          <t>8,62; 13,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,2; 18,35</t>
+          <t>11,83; 17,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,11; 16,9</t>
+          <t>11,43; 16,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,14; 18,81</t>
+          <t>13,06; 18,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,05; 24,45</t>
+          <t>17,82; 24,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,28; 24,65</t>
+          <t>22,13; 27,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,15; 13,57</t>
+          <t>9,98; 13,64</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,88; 14,58</t>
+          <t>10,89; 14,68</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,07; 18,25</t>
+          <t>13,99; 18,05</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,88; 19,95</t>
+          <t>17,87; 21,85</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,83; 13,1</t>
+          <t>8,74; 13,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,33; 14,23</t>
+          <t>8,91; 14,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,89</t>
+          <t>5,25; 8,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,03; 12,67</t>
+          <t>9,49; 14,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,48; 21,3</t>
+          <t>15,24; 21,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,05; 21,65</t>
+          <t>16,07; 21,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,09; 17,23</t>
+          <t>11,59; 17,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,28; 23,3</t>
+          <t>17,7; 22,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,55; 16,31</t>
+          <t>12,74; 16,29</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13,56; 17,38</t>
+          <t>13,39; 17,06</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,21; 12,47</t>
+          <t>9,21; 12,39</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,53; 17,16</t>
+          <t>14,3; 17,43</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,08; 10,26</t>
+          <t>8,13; 10,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,89; 13,31</t>
+          <t>10,88; 13,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,52; 11,59</t>
+          <t>9,42; 11,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,95; 14,48</t>
+          <t>12,41; 14,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,11; 17,59</t>
+          <t>15,08; 17,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,41; 22,29</t>
+          <t>19,51; 22,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,04; 20,78</t>
+          <t>17,92; 20,93</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,48; 20,83</t>
+          <t>19,68; 21,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,95; 13,53</t>
+          <t>11,95; 13,55</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15,6; 17,43</t>
+          <t>15,63; 17,44</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14,23; 15,97</t>
+          <t>14,07; 15,95</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,91; 17,4</t>
+          <t>16,45; 18,23</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28268</t>
+          <t>27871</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37056</t>
+          <t>42449</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65324</t>
+          <t>70320</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20862; 41180</t>
+          <t>20623; 41397</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30223; 54643</t>
+          <t>30075; 54527</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26397; 49611</t>
+          <t>25667; 50388</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19294; 39974</t>
+          <t>20245; 38890</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>39034; 64778</t>
+          <t>40712; 67039</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63258; 95536</t>
+          <t>64346; 96208</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62256; 93481</t>
+          <t>60838; 91667</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29713; 47420</t>
+          <t>33638; 53127</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>67616; 100916</t>
+          <t>65412; 99116</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>101674; 140865</t>
+          <t>99077; 141334</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>93501; 133570</t>
+          <t>92086; 131360</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>53212; 80540</t>
+          <t>57935; 85040</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91091</t>
+          <t>96214</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>126671</t>
+          <t>131610</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>217763</t>
+          <t>227824</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35652; 62751</t>
+          <t>35223; 62028</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42355; 73885</t>
+          <t>40777; 72624</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31304; 55464</t>
+          <t>31209; 56885</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72458; 111667</t>
+          <t>78413; 117995</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74551; 109431</t>
+          <t>75700; 108680</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82134; 118703</t>
+          <t>80882; 120971</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69909; 105567</t>
+          <t>69231; 105344</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>111696; 143132</t>
+          <t>115056; 149878</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>116934; 159351</t>
+          <t>116437; 159927</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>131751; 181269</t>
+          <t>131720; 179133</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>107642; 153624</t>
+          <t>109336; 152860</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>192179; 241598</t>
+          <t>202368; 257005</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46013</t>
+          <t>44714</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>66140</t>
+          <t>65908</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>112153</t>
+          <t>110622</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12140; 30106</t>
+          <t>12075; 30301</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28764; 54663</t>
+          <t>29345; 53952</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19447; 38889</t>
+          <t>19275; 38756</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36011; 58723</t>
+          <t>35195; 56758</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>34838; 60261</t>
+          <t>34136; 60045</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53532; 84034</t>
+          <t>53365; 82418</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30155; 54811</t>
+          <t>30268; 56055</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>55052; 79434</t>
+          <t>55251; 77663</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>51473; 83241</t>
+          <t>52105; 82746</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89702; 128408</t>
+          <t>87850; 128017</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54478; 87173</t>
+          <t>53623; 87166</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>96965; 129115</t>
+          <t>96198; 126105</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62591</t>
+          <t>70159</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>96650</t>
+          <t>106034</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>159241</t>
+          <t>176193</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11396; 28673</t>
+          <t>11530; 29309</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45471; 75189</t>
+          <t>47309; 76568</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49152; 78360</t>
+          <t>48934; 79012</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49071; 80071</t>
+          <t>54320; 90884</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>46757; 76275</t>
+          <t>48411; 76390</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>109659; 147803</t>
+          <t>108763; 147010</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>108718; 147682</t>
+          <t>106783; 146521</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>57673; 125729</t>
+          <t>89766; 122549</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>63652; 96248</t>
+          <t>64653; 96985</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>164490; 211332</t>
+          <t>163138; 209964</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>162022; 213097</t>
+          <t>163568; 214237</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>114923; 188602</t>
+          <t>152947; 202696</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>13931</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26607</t>
+          <t>28204</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>39575</t>
+          <t>42135</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9531; 24056</t>
+          <t>9005; 23364</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17819; 37055</t>
+          <t>18324; 37465</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10606; 26698</t>
+          <t>10005; 26300</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8629; 19235</t>
+          <t>9082; 20325</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16754; 35930</t>
+          <t>16013; 35691</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42429; 69070</t>
+          <t>43424; 68069</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20944; 40455</t>
+          <t>19394; 39186</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20819; 32990</t>
+          <t>22140; 35272</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>30502; 54332</t>
+          <t>29425; 53385</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65763; 97534</t>
+          <t>66533; 99222</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35649; 62111</t>
+          <t>35101; 59008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>32063; 48495</t>
+          <t>34603; 51077</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33660</t>
+          <t>32817</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>44281</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77182</t>
+          <t>77098</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18505; 37380</t>
+          <t>18730; 37961</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>27372; 49457</t>
+          <t>27158; 49159</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32471; 56574</t>
+          <t>33286; 57677</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26330; 43865</t>
+          <t>24442; 42679</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>36116; 60607</t>
+          <t>36742; 60389</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37682; 62396</t>
+          <t>36403; 60407</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52439; 81320</t>
+          <t>53573; 82401</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>36120; 53038</t>
+          <t>36317; 53848</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>58925; 90116</t>
+          <t>60158; 92475</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70298; 103275</t>
+          <t>69257; 104585</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>92332; 131461</t>
+          <t>91642; 132058</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>65613; 90808</t>
+          <t>64789; 90589</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92879</t>
+          <t>103886</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>153030</t>
+          <t>190045</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>245909</t>
+          <t>293931</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>45810; 75286</t>
+          <t>45713; 74754</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>48507; 79849</t>
+          <t>46865; 78568</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>57728; 92304</t>
+          <t>56611; 90909</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>75999; 114365</t>
+          <t>84974; 126557</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>70926; 107853</t>
+          <t>72919; 106274</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>91198; 130544</t>
+          <t>90615; 131392</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>124771; 169053</t>
+          <t>123178; 167999</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>70282; 209321</t>
+          <t>170835; 211523</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>127261; 170047</t>
+          <t>125087; 170983</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>147589; 197834</t>
+          <t>147677; 199116</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>189676; 246027</t>
+          <t>188618; 243343</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>160178; 293741</t>
+          <t>266377; 325725</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>81249</t>
+          <t>91410</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>148357</t>
+          <t>165501</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>229606</t>
+          <t>256912</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>65647; 97461</t>
+          <t>64994; 97812</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>72673; 110893</t>
+          <t>69393; 110333</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>40865; 69184</t>
+          <t>40839; 69002</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>37461; 117687</t>
+          <t>75711; 111817</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>121285; 166895</t>
+          <t>119381; 165367</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>132266; 178359</t>
+          <t>132431; 178960</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>99884; 142379</t>
+          <t>95764; 141166</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>131167; 167221</t>
+          <t>147133; 185789</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>191732; 249063</t>
+          <t>194573; 248814</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>217344; 278528</t>
+          <t>214695; 273453</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>147839; 200150</t>
+          <t>147725; 198778</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>140516; 282568</t>
+          <t>233070; 283928</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>448719</t>
+          <t>481003</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>698033</t>
+          <t>774032</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1146752</t>
+          <t>1255035</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>264894; 336158</t>
+          <t>266224; 332220</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>373017; 456133</t>
+          <t>372736; 457774</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>323257; 393536</t>
+          <t>319716; 394196</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>344105; 500524</t>
+          <t>438177; 522614</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>510656; 594358</t>
+          <t>509670; 596973</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>690758; 793204</t>
+          <t>694203; 793882</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>639480; 736634</t>
+          <t>635291; 741820</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>566674; 762632</t>
+          <t>734684; 817138</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>795588; 900460</t>
+          <t>795572; 901563</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1089810; 1217156</t>
+          <t>1091529; 1218293</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>987151; 1107887</t>
+          <t>976514; 1106741</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>990136; 1238738</t>
+          <t>1194796; 1324056</t>
         </is>
       </c>
     </row>
